--- a/Excel/Language.xlsx
+++ b/Excel/Language.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Unity\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7428E747-EFF6-4072-B37E-5983F6E94AC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B163FFD-AC6D-46D0-B2EB-1FD72B5B56C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SimplifiedChinese" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="126">
   <si>
     <t>SheetName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -65,9 +65,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>GameStart</t>
-  </si>
-  <si>
     <t>开始游戏</t>
   </si>
   <si>
@@ -452,6 +449,45 @@
   <si>
     <t>経験</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoundClear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第{0}关 通过</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Round {0} Clear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ステージ {0} クリア</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TitlePanelGameStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TitlePanelGameSetting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoundClearPanelClear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRESS SETTING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>設定</t>
   </si>
 </sst>
 </file>
@@ -494,10 +530,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -779,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.875" style="1" customWidth="1"/>
@@ -805,7 +844,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -830,7 +869,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -838,21 +877,22 @@
         <v>1001</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -860,10 +900,10 @@
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -871,10 +911,10 @@
         <v>1004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -882,10 +922,10 @@
         <v>1005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -893,10 +933,10 @@
         <v>1006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -904,10 +944,10 @@
         <v>1007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -915,10 +955,10 @@
         <v>1008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -926,10 +966,10 @@
         <v>1009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -937,10 +977,10 @@
         <v>1010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -948,10 +988,10 @@
         <v>1011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -959,10 +999,10 @@
         <v>1012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
@@ -970,10 +1010,10 @@
         <v>1013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.2">
@@ -981,10 +1021,10 @@
         <v>1014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.2">
@@ -992,10 +1032,10 @@
         <v>1015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
@@ -1003,10 +1043,10 @@
         <v>1016</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
@@ -1014,10 +1054,10 @@
         <v>1017</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
@@ -1025,10 +1065,10 @@
         <v>1018</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
@@ -1036,10 +1076,10 @@
         <v>1019</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.2">
@@ -1047,10 +1087,10 @@
         <v>1020</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.2">
@@ -1058,10 +1098,10 @@
         <v>1021</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.2">
@@ -1069,10 +1109,10 @@
         <v>1022</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.2">
@@ -1080,10 +1120,10 @@
         <v>1023</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.2">
@@ -1091,10 +1131,10 @@
         <v>1024</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.2">
@@ -1102,10 +1142,10 @@
         <v>1025</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.2">
@@ -1113,10 +1153,10 @@
         <v>1026</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.2">
@@ -1124,10 +1164,10 @@
         <v>1027</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.2">
@@ -1135,10 +1175,10 @@
         <v>1028</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.2">
@@ -1146,10 +1186,10 @@
         <v>1029</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
@@ -1157,10 +1197,10 @@
         <v>1030</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.2">
@@ -1168,10 +1208,10 @@
         <v>1031</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.2">
@@ -1179,10 +1219,32 @@
         <v>1032</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D36" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B37" s="1">
+        <v>1033</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B38" s="1">
+        <v>1034</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1193,7 +1255,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650FEAEC-B199-4F32-84CE-924FD65588D6}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1217,7 +1279,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -1243,7 +1305,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1255,10 +1317,10 @@
         <v>1001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1267,10 +1329,10 @@
         <v>1002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>106</v>
+        <v>121</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1279,10 +1341,10 @@
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1291,10 +1353,10 @@
         <v>1004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1303,10 +1365,10 @@
         <v>1005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -1315,10 +1377,10 @@
         <v>1006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>110</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -1327,10 +1389,10 @@
         <v>1007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -1339,22 +1401,21 @@
         <v>1008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="1"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="1">
         <v>1009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -1363,10 +1424,10 @@
         <v>1010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -1375,10 +1436,10 @@
         <v>1011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -1387,10 +1448,10 @@
         <v>1012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -1399,10 +1460,10 @@
         <v>1013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -1411,10 +1472,10 @@
         <v>1014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -1423,10 +1484,10 @@
         <v>1015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -1435,10 +1496,10 @@
         <v>1016</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -1447,10 +1508,10 @@
         <v>1017</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -1459,10 +1520,10 @@
         <v>1018</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -1471,10 +1532,10 @@
         <v>1019</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -1483,10 +1544,10 @@
         <v>1020</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -1495,10 +1556,10 @@
         <v>1021</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -1507,10 +1568,10 @@
         <v>1022</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -1519,10 +1580,10 @@
         <v>1023</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -1531,10 +1592,10 @@
         <v>1024</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -1543,10 +1604,10 @@
         <v>1025</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -1555,10 +1616,10 @@
         <v>1026</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -1567,10 +1628,10 @@
         <v>1027</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -1579,10 +1640,10 @@
         <v>1028</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -1591,10 +1652,10 @@
         <v>1029</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -1603,10 +1664,10 @@
         <v>1030</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -1615,10 +1676,10 @@
         <v>1031</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -1627,10 +1688,34 @@
         <v>1032</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1">
+        <v>1033</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1">
+        <v>1034</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1641,7 +1726,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9311664B-7025-4B3E-B6EF-B68E9E4C06CE}">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.875" customWidth="1"/>
@@ -1667,7 +1752,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -1695,7 +1780,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1708,10 +1793,10 @@
         <v>1001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5" s="1"/>
     </row>
@@ -1721,12 +1806,11 @@
         <v>1002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
+        <v>121</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="1"/>
+        <v>124</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
@@ -1734,10 +1818,10 @@
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E7" s="1"/>
     </row>
@@ -1747,10 +1831,10 @@
         <v>1004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E8" s="1"/>
     </row>
@@ -1760,10 +1844,10 @@
         <v>1005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E9" s="1"/>
     </row>
@@ -1773,10 +1857,10 @@
         <v>1006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E10" s="1"/>
     </row>
@@ -1786,10 +1870,10 @@
         <v>1007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -1799,25 +1883,23 @@
         <v>1008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="1"/>
+    <row r="13" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B13" s="1">
         <v>1009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" s="1"/>
+        <v>118</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
@@ -1825,10 +1907,10 @@
         <v>1010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="E14" s="1"/>
     </row>
@@ -1838,10 +1920,10 @@
         <v>1011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E15" s="1"/>
     </row>
@@ -1851,10 +1933,10 @@
         <v>1012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E16" s="1"/>
     </row>
@@ -1864,10 +1946,10 @@
         <v>1013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E17" s="1"/>
     </row>
@@ -1877,10 +1959,10 @@
         <v>1014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E18" s="1"/>
     </row>
@@ -1890,10 +1972,10 @@
         <v>1015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E19" s="1"/>
     </row>
@@ -1903,10 +1985,10 @@
         <v>1016</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E20" s="1"/>
     </row>
@@ -1916,10 +1998,10 @@
         <v>1017</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E21" s="1"/>
     </row>
@@ -1929,10 +2011,10 @@
         <v>1018</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E22" s="1"/>
     </row>
@@ -1942,10 +2024,10 @@
         <v>1019</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E23" s="1"/>
     </row>
@@ -1955,10 +2037,10 @@
         <v>1020</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E24" s="1"/>
     </row>
@@ -1968,10 +2050,10 @@
         <v>1021</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E25" s="1"/>
     </row>
@@ -1981,10 +2063,10 @@
         <v>1022</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E26" s="1"/>
     </row>
@@ -1994,10 +2076,10 @@
         <v>1023</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E27" s="1"/>
     </row>
@@ -2007,10 +2089,10 @@
         <v>1024</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E28" s="1"/>
     </row>
@@ -2020,10 +2102,10 @@
         <v>1025</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E29" s="1"/>
     </row>
@@ -2033,10 +2115,10 @@
         <v>1026</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E30" s="1"/>
     </row>
@@ -2046,10 +2128,10 @@
         <v>1027</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E31" s="1"/>
     </row>
@@ -2059,10 +2141,10 @@
         <v>1028</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E32" s="1"/>
     </row>
@@ -2072,10 +2154,10 @@
         <v>1029</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E33" s="1"/>
     </row>
@@ -2085,10 +2167,10 @@
         <v>1030</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E34" s="1"/>
     </row>
@@ -2098,10 +2180,10 @@
         <v>1031</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E35" s="1"/>
     </row>
@@ -2111,12 +2193,38 @@
         <v>1032</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1">
+        <v>1033</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1">
+        <v>1034</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E38" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Excel/Language.xlsx
+++ b/Excel/Language.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Unity\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B163FFD-AC6D-46D0-B2EB-1FD72B5B56C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924F851D-02CD-428A-907F-9C78639E6BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SimplifiedChinese" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="130">
   <si>
     <t>SheetName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -488,6 +488,22 @@
   </si>
   <si>
     <t>設定</t>
+  </si>
+  <si>
+    <t>RoleSelectPanelTitle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选 择 角 色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S E L E C T  P L A Y E R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ロ ー ル の 選 択</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -818,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.875" style="1" customWidth="1"/>
@@ -895,15 +911,16 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -911,10 +928,10 @@
         <v>1004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -922,10 +939,10 @@
         <v>1005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -933,10 +950,10 @@
         <v>1006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -944,10 +961,10 @@
         <v>1007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -955,10 +972,10 @@
         <v>1008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -966,10 +983,10 @@
         <v>1009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>117</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -977,10 +994,10 @@
         <v>1010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -988,10 +1005,10 @@
         <v>1011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -999,10 +1016,10 @@
         <v>1012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
@@ -1010,10 +1027,10 @@
         <v>1013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.2">
@@ -1021,10 +1038,10 @@
         <v>1014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.2">
@@ -1032,10 +1049,10 @@
         <v>1015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
@@ -1043,10 +1060,10 @@
         <v>1016</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
@@ -1054,10 +1071,10 @@
         <v>1017</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
@@ -1065,10 +1082,10 @@
         <v>1018</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
@@ -1076,10 +1093,10 @@
         <v>1019</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.2">
@@ -1087,10 +1104,10 @@
         <v>1020</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.2">
@@ -1098,10 +1115,10 @@
         <v>1021</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.2">
@@ -1109,10 +1126,10 @@
         <v>1022</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.2">
@@ -1120,10 +1137,10 @@
         <v>1023</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.2">
@@ -1131,10 +1148,10 @@
         <v>1024</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.2">
@@ -1142,10 +1159,10 @@
         <v>1025</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.2">
@@ -1153,10 +1170,10 @@
         <v>1026</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.2">
@@ -1164,10 +1181,10 @@
         <v>1027</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.2">
@@ -1175,10 +1192,10 @@
         <v>1028</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.2">
@@ -1186,10 +1203,10 @@
         <v>1029</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
@@ -1197,10 +1214,10 @@
         <v>1030</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.2">
@@ -1208,10 +1225,10 @@
         <v>1031</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.2">
@@ -1219,10 +1236,10 @@
         <v>1032</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.2">
@@ -1230,10 +1247,10 @@
         <v>1033</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.2">
@@ -1241,9 +1258,20 @@
         <v>1034</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B39" s="1">
+        <v>1035</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1255,7 +1283,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650FEAEC-B199-4F32-84CE-924FD65588D6}">
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1341,10 +1369,10 @@
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1353,10 +1381,10 @@
         <v>1004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1365,10 +1393,10 @@
         <v>1005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -1377,10 +1405,10 @@
         <v>1006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -1389,10 +1417,10 @@
         <v>1007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>114</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -1401,33 +1429,33 @@
         <v>1008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>1009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="1">
         <v>1010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -1436,10 +1464,10 @@
         <v>1011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -1448,10 +1476,10 @@
         <v>1012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -1460,10 +1488,10 @@
         <v>1013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -1472,10 +1500,10 @@
         <v>1014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -1484,10 +1512,10 @@
         <v>1015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -1496,10 +1524,10 @@
         <v>1016</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -1508,10 +1536,10 @@
         <v>1017</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -1520,10 +1548,10 @@
         <v>1018</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -1532,10 +1560,10 @@
         <v>1019</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -1544,10 +1572,10 @@
         <v>1020</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
@@ -1556,10 +1584,10 @@
         <v>1021</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
@@ -1568,10 +1596,10 @@
         <v>1022</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
@@ -1580,10 +1608,10 @@
         <v>1023</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
@@ -1592,10 +1620,10 @@
         <v>1024</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
@@ -1604,10 +1632,10 @@
         <v>1025</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
@@ -1616,10 +1644,10 @@
         <v>1026</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -1628,10 +1656,10 @@
         <v>1027</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
@@ -1640,10 +1668,10 @@
         <v>1028</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -1652,10 +1680,10 @@
         <v>1029</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -1664,10 +1692,10 @@
         <v>1030</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -1676,10 +1704,10 @@
         <v>1031</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -1688,10 +1716,10 @@
         <v>1032</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -1700,10 +1728,10 @@
         <v>1033</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -1712,9 +1740,21 @@
         <v>1034</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1">
+        <v>1035</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1726,7 +1766,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9311664B-7025-4B3E-B6EF-B68E9E4C06CE}">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.875" customWidth="1"/>
@@ -1818,12 +1858,11 @@
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>126</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" s="1"/>
+        <v>128</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
@@ -1831,10 +1870,10 @@
         <v>1004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E8" s="1"/>
     </row>
@@ -1844,10 +1883,10 @@
         <v>1005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E9" s="1"/>
     </row>
@@ -1857,10 +1896,10 @@
         <v>1006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E10" s="1"/>
     </row>
@@ -1870,10 +1909,10 @@
         <v>1007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -1883,36 +1922,36 @@
         <v>1008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>1009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="1"/>
+        <v>86</v>
+      </c>
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="1">
         <v>1010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" s="1"/>
+        <v>118</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
@@ -1920,10 +1959,10 @@
         <v>1011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E15" s="1"/>
     </row>
@@ -1933,10 +1972,10 @@
         <v>1012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E16" s="1"/>
     </row>
@@ -1946,10 +1985,10 @@
         <v>1013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E17" s="1"/>
     </row>
@@ -1959,10 +1998,10 @@
         <v>1014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E18" s="1"/>
     </row>
@@ -1972,10 +2011,10 @@
         <v>1015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" s="1"/>
     </row>
@@ -1985,10 +2024,10 @@
         <v>1016</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E20" s="1"/>
     </row>
@@ -1998,10 +2037,10 @@
         <v>1017</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E21" s="1"/>
     </row>
@@ -2011,10 +2050,10 @@
         <v>1018</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E22" s="1"/>
     </row>
@@ -2024,10 +2063,10 @@
         <v>1019</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E23" s="1"/>
     </row>
@@ -2037,10 +2076,10 @@
         <v>1020</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E24" s="1"/>
     </row>
@@ -2050,10 +2089,10 @@
         <v>1021</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E25" s="1"/>
     </row>
@@ -2063,10 +2102,10 @@
         <v>1022</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E26" s="1"/>
     </row>
@@ -2076,10 +2115,10 @@
         <v>1023</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E27" s="1"/>
     </row>
@@ -2089,10 +2128,10 @@
         <v>1024</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E28" s="1"/>
     </row>
@@ -2102,10 +2141,10 @@
         <v>1025</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E29" s="1"/>
     </row>
@@ -2115,10 +2154,10 @@
         <v>1026</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E30" s="1"/>
     </row>
@@ -2128,10 +2167,10 @@
         <v>1027</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E31" s="1"/>
     </row>
@@ -2141,10 +2180,10 @@
         <v>1028</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E32" s="1"/>
     </row>
@@ -2154,10 +2193,10 @@
         <v>1029</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E33" s="1"/>
     </row>
@@ -2167,10 +2206,10 @@
         <v>1030</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E34" s="1"/>
     </row>
@@ -2180,10 +2219,10 @@
         <v>1031</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E35" s="1"/>
     </row>
@@ -2193,10 +2232,10 @@
         <v>1032</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E36" s="1"/>
     </row>
@@ -2206,10 +2245,10 @@
         <v>1033</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E37" s="1"/>
     </row>
@@ -2219,12 +2258,25 @@
         <v>1034</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1">
+        <v>1035</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E38" s="1"/>
+      <c r="E39" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Excel/Language.xlsx
+++ b/Excel/Language.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Unity\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{924F851D-02CD-428A-907F-9C78639E6BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A98579-637F-4A2C-9639-F0F2530E0D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SimplifiedChinese" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="162">
   <si>
     <t>SheetName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -65,444 +65,571 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>RoleNameCody</t>
+  </si>
+  <si>
+    <t>科迪</t>
+  </si>
+  <si>
+    <t>RoleNameGuy</t>
+  </si>
+  <si>
+    <t>凯</t>
+  </si>
+  <si>
+    <t>RoleNameHagger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哈格</t>
+  </si>
+  <si>
+    <t>RoleDescCody</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>街头霸王，刀法精湛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleDescGuy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>忍者末裔，健步如飞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoleDescHagger</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴躁市长，背摔达人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainPanelPlayer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玩家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainPanelEnemy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainPanelStage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>关卡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainPanelLife</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainPanelLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainPanelExp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talk1001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>呵呵，老子叫达姆德</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这片儿的扛把子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给老子跪下！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>很好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老子看好你</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跟老子混吧，老子保你荣华富贵！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>呵呵，老子逗你玩你竟然也相信。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滚回家吃奶去吧，唐氏儿！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>呵呵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老子给你脸你不要脸</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老子再说一遍，这片儿老子天下第一！你服不服？！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哇呀呀呀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>给老子死！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不跪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大哥，统一黑白两道！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>做梦，今天你必须死！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你算个嘚！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大哥，我服了！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talk1002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talk1003</t>
+  </si>
+  <si>
+    <t>Talk1004</t>
+  </si>
+  <si>
+    <t>Talk1005</t>
+  </si>
+  <si>
+    <t>Talk1006</t>
+  </si>
+  <si>
+    <t>Talk1007</t>
+  </si>
+  <si>
+    <t>Talk1008</t>
+  </si>
+  <si>
+    <t>Talk1009</t>
+  </si>
+  <si>
+    <t>Talk1010</t>
+  </si>
+  <si>
+    <t>Talk1011</t>
+  </si>
+  <si>
+    <t>Talk1012</t>
+  </si>
+  <si>
+    <t>Talk1013</t>
+  </si>
+  <si>
+    <t>Talk1003_Select1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talk1003_Select2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talk1006_Select1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talk1006_Select2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talk1011_Select1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Talk1011_Select2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SimplifiedChinese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>English</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRESS START</t>
+  </si>
+  <si>
+    <t>CODY</t>
+  </si>
+  <si>
+    <t>GUY</t>
+  </si>
+  <si>
+    <t>HAGGER</t>
+  </si>
+  <si>
+    <t>A TOUGH STREET FIGHTER WHO IS\nSKILLED WITH KNIVES.</t>
+  </si>
+  <si>
+    <t>DESCENDED FROM NINJA HE POSSESSES\nINCREDIBLE  AGILITY.</t>
+  </si>
+  <si>
+    <t>THE HOT-TEMPERED WRESTLER AND MAYOR\nOF METRO CITY.</t>
+  </si>
+  <si>
+    <t>PLAYER</t>
+  </si>
+  <si>
+    <t>ENEMY</t>
+  </si>
+  <si>
+    <t>RD</t>
+  </si>
+  <si>
+    <t>PL</t>
+  </si>
+  <si>
+    <t>LEVEL</t>
+  </si>
+  <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>HEN-HEN. I AM DAMND.</t>
+  </si>
+  <si>
+    <t>RULER OF THIS CITY.</t>
+  </si>
+  <si>
+    <t>BOW DOWN BEFORE ME!</t>
+  </si>
+  <si>
+    <t>I AM SUPERIOR.</t>
+  </si>
+  <si>
+    <t>MAYBE YOU'RE STRONGER THAN YOU LOOK.</t>
+  </si>
+  <si>
+    <t>WHY DON'T YOU JOIN US?</t>
+  </si>
+  <si>
+    <t>HEN-HEH. I DON'T BELIEVE YOU.</t>
+  </si>
+  <si>
+    <t>YOU'RE TOO MUCH OF A MAMA'S BOY.</t>
+  </si>
+  <si>
+    <t>YOU DARE REFUSE THE MAD GREA GANG?</t>
+  </si>
+  <si>
+    <t>WAAAAA!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DON'T YOU KNOW I RULE THE STREETS!?</t>
+  </si>
+  <si>
+    <t>ARGHHHHH!</t>
+  </si>
+  <si>
+    <t>THOSE WHO OFFEND ME MUST DIE!</t>
+  </si>
+  <si>
+    <t>YES</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LANGUAGE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Japanese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ゲームをスタート</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>コーディ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>甲斐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ヘイガー</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ストリートファイター、素晴らしいナイフスキル</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飛ぶのと同じ速さで歩く忍者の末裔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>短気な市長であり、裏レスリングの達人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>プレーヤー</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>フェーズ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等級</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>経験</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoundClear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第{0}关 通过</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Round {0} Clear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ステージ {0} クリア</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TitlePanelGameStart</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TitlePanelGameSetting</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RoundClearPanelClear</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>设置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRESS SETTING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>設定</t>
+  </si>
+  <si>
+    <t>RoleSelectPanelTitle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>选 择 角 色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S E L E C T  P L A Y E R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ロ ー ル の 選 択</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VersionPanelCheckVersion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正在进行版本验证…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>版本验证失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VersionPaneCheckVersionError</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VersionPaneCheckVersionComplete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>版本验证成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正在进行版本解析...</t>
+  </si>
+  <si>
+    <t>VersionPanelVersionAnalyze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VersionPanelVersionAnalyzeError</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>版本解析失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VersionPanelVersionAnalyzeComplete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>版本解析成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正在下载更新文件...({0}/{1})</t>
+  </si>
+  <si>
+    <t>VersionPanelDownloadFiles</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>下载文件失败</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VersionPanelDownloadFilesError</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Version verification in progress…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Version verification failed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Version verification successful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Version parsing in progress...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Version parsing failed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Version parsing successful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Downloading update files...({0}/{1})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Download file failed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>バージョン検証中…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>バージョンの検証に失敗しました</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>バージョンの検証に成功しました</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>バージョン解決中...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>バージョン解決に失敗しました</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>バージョン解決に成功しました</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新ファイルをダウンロードしています...({0}/{1})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ファイルのダウンロードに失敗しました</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>开始游戏</t>
-  </si>
-  <si>
-    <t>RoleNameCody</t>
-  </si>
-  <si>
-    <t>科迪</t>
-  </si>
-  <si>
-    <t>RoleNameGuy</t>
-  </si>
-  <si>
-    <t>凯</t>
-  </si>
-  <si>
-    <t>RoleNameHagger</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>哈格</t>
-  </si>
-  <si>
-    <t>RoleDescCody</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>街头霸王，刀法精湛</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RoleDescGuy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>忍者末裔，健步如飞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RoleDescHagger</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴躁市长，背摔达人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainPanelPlayer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玩家</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainPanelEnemy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>敌人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainPanelStage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>关卡</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainPanelLife</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainPanelLevel</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MainPanelExp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>经验</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Talk1001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>呵呵，老子叫达姆德</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>这片儿的扛把子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>给老子跪下！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>很好</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>老子看好你</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>跟老子混吧，老子保你荣华富贵！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>呵呵，老子逗你玩你竟然也相信。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>滚回家吃奶去吧，唐氏儿！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>呵呵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>老子给你脸你不要脸</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>老子再说一遍，这片儿老子天下第一！你服不服？！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>哇呀呀呀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>给老子死！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>跪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不跪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大哥，统一黑白两道！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>做梦，今天你必须死！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你算个嘚！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大哥，我服了！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Talk1002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Talk1003</t>
-  </si>
-  <si>
-    <t>Talk1004</t>
-  </si>
-  <si>
-    <t>Talk1005</t>
-  </si>
-  <si>
-    <t>Talk1006</t>
-  </si>
-  <si>
-    <t>Talk1007</t>
-  </si>
-  <si>
-    <t>Talk1008</t>
-  </si>
-  <si>
-    <t>Talk1009</t>
-  </si>
-  <si>
-    <t>Talk1010</t>
-  </si>
-  <si>
-    <t>Talk1011</t>
-  </si>
-  <si>
-    <t>Talk1012</t>
-  </si>
-  <si>
-    <t>Talk1013</t>
-  </si>
-  <si>
-    <t>Talk1003_Select1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Talk1003_Select2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Talk1006_Select1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Talk1006_Select2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Talk1011_Select1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Talk1011_Select2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SimplifiedChinese</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>English</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRESS START</t>
-  </si>
-  <si>
-    <t>CODY</t>
-  </si>
-  <si>
-    <t>GUY</t>
-  </si>
-  <si>
-    <t>HAGGER</t>
-  </si>
-  <si>
-    <t>A TOUGH STREET FIGHTER WHO IS\nSKILLED WITH KNIVES.</t>
-  </si>
-  <si>
-    <t>DESCENDED FROM NINJA HE POSSESSES\nINCREDIBLE  AGILITY.</t>
-  </si>
-  <si>
-    <t>THE HOT-TEMPERED WRESTLER AND MAYOR\nOF METRO CITY.</t>
-  </si>
-  <si>
-    <t>PLAYER</t>
-  </si>
-  <si>
-    <t>ENEMY</t>
-  </si>
-  <si>
-    <t>RD</t>
-  </si>
-  <si>
-    <t>PL</t>
-  </si>
-  <si>
-    <t>LEVEL</t>
-  </si>
-  <si>
-    <t>EXP</t>
-  </si>
-  <si>
-    <t>HEN-HEN. I AM DAMND.</t>
-  </si>
-  <si>
-    <t>RULER OF THIS CITY.</t>
-  </si>
-  <si>
-    <t>BOW DOWN BEFORE ME!</t>
-  </si>
-  <si>
-    <t>I AM SUPERIOR.</t>
-  </si>
-  <si>
-    <t>MAYBE YOU'RE STRONGER THAN YOU LOOK.</t>
-  </si>
-  <si>
-    <t>WHY DON'T YOU JOIN US?</t>
-  </si>
-  <si>
-    <t>HEN-HEH. I DON'T BELIEVE YOU.</t>
-  </si>
-  <si>
-    <t>YOU'RE TOO MUCH OF A MAMA'S BOY.</t>
-  </si>
-  <si>
-    <t>YOU DARE REFUSE THE MAD GREA GANG?</t>
-  </si>
-  <si>
-    <t>WAAAAA!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DON'T YOU KNOW I RULE THE STREETS!?</t>
-  </si>
-  <si>
-    <t>ARGHHHHH!</t>
-  </si>
-  <si>
-    <t>THOSE WHO OFFEND ME MUST DIE!</t>
-  </si>
-  <si>
-    <t>YES</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>NO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LANGUAGE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Japanese</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ゲームをスタート</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>コーディ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>甲斐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ヘイガー</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ストリートファイター、素晴らしいナイフスキル</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>飛ぶのと同じ速さで歩く忍者の末裔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>短気な市長であり、裏レスリングの達人</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>プレーヤー</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>敵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>フェーズ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等級</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>経験</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RoundClear</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第{0}关 通过</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Round {0} Clear</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ステージ {0} クリア</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TitlePanelGameStart</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TitlePanelGameSetting</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RoundClearPanelClear</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRESS SETTING</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>設定</t>
-  </si>
-  <si>
-    <t>RoleSelectPanelTitle</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选 择 角 色</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>S E L E C T  P L A Y E R</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ロ ー ル の 選 択</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -834,7 +961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.875" style="1" customWidth="1"/>
@@ -844,7 +971,7 @@
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -858,9 +985,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -872,7 +999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -883,319 +1010,335 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>1001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
         <v>1004</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B9" s="1">
         <v>1005</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
         <v>1006</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B11" s="1">
         <v>1007</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B12" s="1">
         <v>1008</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B13" s="1">
         <v>1009</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>1010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>1011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>1012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>1013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>1014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>1015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>1016</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>1017</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>34</v>
+        <v>144</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B22" s="1">
         <v>1018</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B23" s="1">
         <v>1019</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B24" s="1">
         <v>1020</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B25" s="1">
         <v>1021</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B26" s="1">
         <v>1022</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B27" s="1">
         <v>1023</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B28" s="1">
         <v>1024</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B29" s="1">
         <v>1025</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B30" s="1">
         <v>1026</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B31" s="1">
         <v>1027</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B32" s="1">
         <v>1028</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.2">
@@ -1203,10 +1346,10 @@
         <v>1029</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
@@ -1214,10 +1357,10 @@
         <v>1030</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.2">
@@ -1225,10 +1368,10 @@
         <v>1031</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.2">
@@ -1236,10 +1379,10 @@
         <v>1032</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.2">
@@ -1247,10 +1390,10 @@
         <v>1033</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.2">
@@ -1258,10 +1401,10 @@
         <v>1034</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.2">
@@ -1269,10 +1412,98 @@
         <v>1035</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D39" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B40" s="1">
+        <v>1036</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B41" s="1">
+        <v>1037</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B42" s="1">
+        <v>1038</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B43" s="1">
+        <v>1039</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B44" s="1">
+        <v>1040</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B45" s="1">
+        <v>1041</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B46" s="1">
+        <v>1042</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B47" s="1">
+        <v>1043</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1283,7 +1514,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650FEAEC-B199-4F32-84CE-924FD65588D6}">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1291,7 +1522,7 @@
     <col min="4" max="4" width="68.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1305,9 +1536,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -1319,7 +1550,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -1331,431 +1562,535 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>1004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>1005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>1006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>1007</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>1008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>1009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>1010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+        <v>153</v>
+      </c>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>1011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>1012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>1013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>1014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>1015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>1016</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+        <v>159</v>
+      </c>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>1017</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>34</v>
+        <v>144</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
+        <v>160</v>
+      </c>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="1">
-        <v>1018</v>
+        <v>1010</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
-        <v>1019</v>
+        <v>1011</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
-        <v>1022</v>
+        <v>1014</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
-        <v>1023</v>
+        <v>1015</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
-        <v>1024</v>
+        <v>1016</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
-        <v>1025</v>
+        <v>1017</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
-        <v>1026</v>
+        <v>1018</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
-        <v>1027</v>
+        <v>1019</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
-        <v>1028</v>
+        <v>1020</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
-        <v>1029</v>
+        <v>1021</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
-        <v>1030</v>
+        <v>1022</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="1">
-        <v>1031</v>
+        <v>1023</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
-        <v>1032</v>
+        <v>1024</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
-        <v>1033</v>
+        <v>1025</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
-        <v>1034</v>
+        <v>1026</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
+        <v>1027</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1">
+        <v>1028</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1">
+        <v>1029</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1">
+        <v>1030</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1">
+        <v>1031</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1">
+        <v>1032</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1">
+        <v>1033</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1">
+        <v>1034</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1">
         <v>1035</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>101</v>
+      <c r="C47" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1766,7 +2101,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9311664B-7025-4B3E-B6EF-B68E9E4C06CE}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.875" customWidth="1"/>
@@ -1792,7 +2127,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -1820,7 +2155,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1833,10 +2168,10 @@
         <v>1001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5" s="1"/>
     </row>
@@ -1846,10 +2181,10 @@
         <v>1002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -1858,10 +2193,10 @@
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -1870,10 +2205,10 @@
         <v>1004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E8" s="1"/>
     </row>
@@ -1883,10 +2218,10 @@
         <v>1005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E9" s="1"/>
     </row>
@@ -1896,10 +2231,10 @@
         <v>1006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E10" s="1"/>
     </row>
@@ -1909,10 +2244,10 @@
         <v>1007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E11" s="1"/>
     </row>
@@ -1922,10 +2257,10 @@
         <v>1008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E12" s="1"/>
     </row>
@@ -1935,23 +2270,25 @@
         <v>1009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>1010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>118</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
@@ -1959,10 +2296,10 @@
         <v>1011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="E15" s="1"/>
     </row>
@@ -1972,10 +2309,10 @@
         <v>1012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>76</v>
+        <v>147</v>
       </c>
       <c r="E16" s="1"/>
     </row>
@@ -1985,10 +2322,10 @@
         <v>1013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="E17" s="1"/>
     </row>
@@ -1998,10 +2335,10 @@
         <v>1014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="E18" s="1"/>
     </row>
@@ -2011,10 +2348,10 @@
         <v>1015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>18</v>
+        <v>139</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="E19" s="1"/>
     </row>
@@ -2024,10 +2361,10 @@
         <v>1016</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="E20" s="1"/>
     </row>
@@ -2037,25 +2374,23 @@
         <v>1017</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>34</v>
+        <v>144</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
+    <row r="22" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="1">
         <v>1018</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="1"/>
+        <v>117</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
@@ -2063,10 +2398,10 @@
         <v>1019</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E23" s="1"/>
     </row>
@@ -2076,10 +2411,10 @@
         <v>1020</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E24" s="1"/>
     </row>
@@ -2089,10 +2424,10 @@
         <v>1021</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E25" s="1"/>
     </row>
@@ -2102,10 +2437,10 @@
         <v>1022</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="E26" s="1"/>
     </row>
@@ -2115,10 +2450,10 @@
         <v>1023</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E27" s="1"/>
     </row>
@@ -2128,10 +2463,10 @@
         <v>1024</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E28" s="1"/>
     </row>
@@ -2141,10 +2476,10 @@
         <v>1025</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E29" s="1"/>
     </row>
@@ -2154,10 +2489,10 @@
         <v>1026</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="E30" s="1"/>
     </row>
@@ -2167,10 +2502,10 @@
         <v>1027</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E31" s="1"/>
     </row>
@@ -2180,10 +2515,10 @@
         <v>1028</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E32" s="1"/>
     </row>
@@ -2193,10 +2528,10 @@
         <v>1029</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E33" s="1"/>
     </row>
@@ -2206,10 +2541,10 @@
         <v>1030</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E34" s="1"/>
     </row>
@@ -2219,10 +2554,10 @@
         <v>1031</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E35" s="1"/>
     </row>
@@ -2232,10 +2567,10 @@
         <v>1032</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E36" s="1"/>
     </row>
@@ -2245,10 +2580,10 @@
         <v>1033</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E37" s="1"/>
     </row>
@@ -2258,10 +2593,10 @@
         <v>1034</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E38" s="1"/>
     </row>
@@ -2271,12 +2606,116 @@
         <v>1035</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1">
+        <v>1036</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E40" s="1"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1">
+        <v>1037</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E41" s="1"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1">
+        <v>1038</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E42" s="1"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1">
+        <v>1039</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E43" s="1"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1">
+        <v>1040</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E44" s="1"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1">
+        <v>1041</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E45" s="1"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1">
+        <v>1042</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E46" s="1"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1">
+        <v>1043</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E47" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Excel/Language.xlsx
+++ b/Excel/Language.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Unity\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A98579-637F-4A2C-9639-F0F2530E0D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA22FB9C-762E-4E30-B8C0-336478E978BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9465" yWindow="1260" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SimplifiedChinese" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="233">
   <si>
     <t>SheetName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -204,10 +207,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>哇呀呀呀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>给老子死！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -631,6 +630,241 @@
   <si>
     <t>开始游戏</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>THIS IS METRO CITY.\r\nWITHIN THE WALLS OF THE\r\nCITY LIVES</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TitlePanelStory1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>THE DAUGHTER OF THE\r\nMAYOR.JESSICA. HER\r\nBEAUTY RADI -</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TitlePanelStory2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATES THROUGHOUT THE\r\nCITY AND GIVES THE\r\nCITIZENS THE</t>
+  </si>
+  <si>
+    <t>POWER TO SURVIVE.BUT\r\nNOW A VILLAIN ATTEMPTS\r\nTO HAVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> THIS BEACON OF LIGHT ALL\r\nTO HIMSELF.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I CAN'T BELIEVE THAT I'VE\r\nACTUALLY FALLEN IN LOVE</t>
+  </si>
+  <si>
+    <t>WITH THE GIRL.SHE WILL\r\nBE MINE....</t>
+  </si>
+  <si>
+    <t>A COUPLE DAYS LATER...</t>
+  </si>
+  <si>
+    <t>WHAT?! JESSICA... KIDNAPPED...!?!</t>
+  </si>
+  <si>
+    <t>WAHT HAVE YOU DONE TO\r\nHER. CODY?</t>
+  </si>
+  <si>
+    <t>ME?!! THIS IS THE WORK OF\r\nTHE MAD GEAR GANG.</t>
+  </si>
+  <si>
+    <t>WAHT DO YOU THINK. GUY?</t>
+  </si>
+  <si>
+    <t>YES THERE'S NOT A\r\nMOMENT TO SPARE LET'S\r\nGO!</t>
+  </si>
+  <si>
+    <t>TitlePanelStory3</t>
+  </si>
+  <si>
+    <t>TitlePanelStory4</t>
+  </si>
+  <si>
+    <t>TitlePanelStory5</t>
+  </si>
+  <si>
+    <t>TitlePanelStory6</t>
+  </si>
+  <si>
+    <t>TitlePanelStory7</t>
+  </si>
+  <si>
+    <t>TitlePanelStory8</t>
+  </si>
+  <si>
+    <t>TitlePanelStory9</t>
+  </si>
+  <si>
+    <t>TitlePanelStory10</t>
+  </si>
+  <si>
+    <t>TitlePanelStory11</t>
+  </si>
+  <si>
+    <t>TitlePanelStory12</t>
+  </si>
+  <si>
+    <t>TitlePanelStory13</t>
+  </si>
+  <si>
+    <t>但现在，一个恶棍企图将这盏明灯据为己有。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赋予市民生存的力量。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>几天后……</t>
+  </si>
+  <si>
+    <t>科迪，你对杰西卡做了什么？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凯，你怎么看？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>她太美了……</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">什么？！杰西卡……被绑架了……！？！ </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>她是我的……</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>她的美貌像明灯一样照耀着整个城市，</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>市长哈格的女儿杰西卡就住在这里。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我？别开玩笑了，这是亚义奴魔干的好事！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>该死的亚义奴魔，一刻也不能耽误，我们走！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这里是地铁市，</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ここは地下都市で、</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>市長の娘ジェシカが市内に住んでいる。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>彼女の美貌は明かりのように街全体に照らし、</t>
+  </si>
+  <si>
+    <t>市民に生きる力を与えている。</t>
+  </si>
+  <si>
+    <t>しかし今、悪党がこの明かりを独占しようとしている。</t>
+  </si>
+  <si>
+    <t>彼女はとても綺麗だ……</t>
+  </si>
+  <si>
+    <t>彼女は私の……</t>
+  </si>
+  <si>
+    <t>数日後……</t>
+  </si>
+  <si>
+    <t>なにジェシカ……誘拐された……！？！</t>
+  </si>
+  <si>
+    <t>コーディ、ジェシカに何をしたの？</t>
+  </si>
+  <si>
+    <t>私？冗談じゃねえよ、これはアユインマカンの仕業だぞ！</t>
+  </si>
+  <si>
+    <t>ケイ、どう思う？</t>
+  </si>
+  <si>
+    <t>このくそったれのヤイヌマ、一刻も無駄にせず、行くぞ！</t>
+  </si>
+  <si>
+    <t>はは、俺の名はダムドだ</t>
+  </si>
+  <si>
+    <t>このエリアのトップ</t>
+  </si>
+  <si>
+    <t>お前はお前に跪け！</t>
+  </si>
+  <si>
+    <t>いいですね</t>
+  </si>
+  <si>
+    <t>老子は君を信じている</t>
+  </si>
+  <si>
+    <t>俺の元に付いてくんな、俺が君を栄華富贵させてやる！</t>
+  </si>
+  <si>
+    <t>へへ、俺が冗談言ってたのに信じちゃったのか。</t>
+  </si>
+  <si>
+    <t>家に帰って母乳を飲め、ダウン症の子！</t>
+  </si>
+  <si>
+    <t>へへ</t>
+  </si>
+  <si>
+    <t>お前、俺がお前に情けをかけたのに、情け知らずだな</t>
+  </si>
+  <si>
+    <t>老子がもう一度言うが、ここのところは老子が天下一だ！お前の認めようか？！</t>
+  </si>
+  <si>
+    <t>啊啊啊啊啊啊啊！</t>
+  </si>
+  <si>
+    <t>あああああああ！</t>
+  </si>
+  <si>
+    <t>老子に死ね！</t>
+  </si>
+  <si>
+    <t>ひざまずいて</t>
+  </si>
+  <si>
+    <t>ひざまずいていない</t>
+  </si>
+  <si>
+    <t>兄貴、黒と白を統一するぞ！</t>
+  </si>
+  <si>
+    <t>夢で、今日お前は死ね！</t>
+  </si>
+  <si>
+    <t>兄貴、お前にはかないません！</t>
+  </si>
+  <si>
+    <t>お前なんか屁でもない！</t>
   </si>
 </sst>
 </file>
@@ -961,17 +1195,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.875" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="28.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30" style="1" customWidth="1"/>
+    <col min="4" max="4" width="38.75" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -985,9 +1219,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -999,7 +1233,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1010,150 +1244,153 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B5" s="1">
         <v>1001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>1004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>1005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>1006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>25</v>
+        <v>177</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>1007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>178</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>1008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>179</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>1009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>1010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>129</v>
+        <v>181</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>1011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>1012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E16" s="1"/>
+        <v>190</v>
+      </c>
     </row>
     <row r="17" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
@@ -1161,12 +1398,11 @@
         <v>1013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E17" s="1"/>
+        <v>197</v>
+      </c>
     </row>
     <row r="18" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
@@ -1174,12 +1410,11 @@
         <v>1014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E18" s="1"/>
+        <v>191</v>
+      </c>
     </row>
     <row r="19" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
@@ -1187,12 +1422,11 @@
         <v>1015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19" s="1"/>
+        <v>198</v>
+      </c>
     </row>
     <row r="20" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
@@ -1200,35 +1434,32 @@
         <v>1016</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="1"/>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B21" s="1">
         <v>1017</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E21" s="1"/>
+        <v>22</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B22" s="1">
         <v>1018</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -1236,10 +1467,10 @@
         <v>1019</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -1247,10 +1478,10 @@
         <v>1020</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -1258,10 +1489,10 @@
         <v>1021</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -1269,241 +1500,400 @@
         <v>1022</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>1023</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+        <v>129</v>
+      </c>
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>1024</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>1025</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>1026</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>1027</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1"/>
       <c r="B32" s="1">
         <v>1028</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1"/>
       <c r="B33" s="1">
         <v>1029</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1"/>
       <c r="B34" s="1">
         <v>1030</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>57</v>
+        <v>143</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B35" s="1">
         <v>1031</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B36" s="1">
         <v>1032</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B37" s="1">
         <v>1033</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B38" s="1">
         <v>1034</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B39" s="1">
         <v>1035</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B40" s="1">
         <v>1036</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B41" s="1">
         <v>1037</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B42" s="1">
         <v>1038</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B43" s="1">
         <v>1039</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B44" s="1">
         <v>1040</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B45" s="1">
         <v>1041</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B46" s="1">
         <v>1042</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B47" s="1">
         <v>1043</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B48" s="1">
+        <v>1044</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B49" s="1">
+        <v>1045</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B50" s="1">
+        <v>1046</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B51" s="1">
+        <v>1047</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B52" s="1">
+        <v>1048</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B53" s="1">
+        <v>1049</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B54" s="1">
+        <v>1050</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B55" s="1">
+        <v>1051</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B56" s="1">
+        <v>1052</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B57" s="1">
+        <v>1053</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B58" s="1">
+        <v>1054</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B59" s="1">
+        <v>1055</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B60" s="1">
+        <v>1056</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1514,7 +1904,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650FEAEC-B199-4F32-84CE-924FD65588D6}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1522,7 +1912,7 @@
     <col min="4" max="4" width="68.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1536,9 +1926,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -1550,7 +1940,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -1562,160 +1952,157 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>1004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>1005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>1006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>25</v>
+        <v>177</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>1007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>178</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>1008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>179</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>1009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>1010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>129</v>
+        <v>181</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>1011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>1012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E16" s="1"/>
+        <v>209</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
@@ -1723,12 +2110,11 @@
         <v>1013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E17" s="1"/>
+        <v>210</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
@@ -1736,12 +2122,11 @@
         <v>1014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="E18" s="1"/>
+        <v>211</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
@@ -1749,348 +2134,509 @@
         <v>1015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E19" s="1"/>
+        <v>212</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
-        <v>1016</v>
+        <v>1003</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E20" s="1"/>
+        <v>127</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
-        <v>1017</v>
+        <v>1004</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E21" s="1"/>
-    </row>
-    <row r="22" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1"/>
       <c r="B22" s="1">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>108</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="E27" s="1"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="E28" s="1"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>86</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="E29" s="1"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>87</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="E30" s="1"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>88</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="E31" s="1"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>57</v>
+        <v>143</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="1"/>
+        <v>159</v>
+      </c>
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B35" s="1">
-        <v>1023</v>
+        <v>1010</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
-        <v>1024</v>
+        <v>1011</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
-        <v>1025</v>
+        <v>1012</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
-        <v>1026</v>
+        <v>1013</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
-        <v>1027</v>
+        <v>1014</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
-        <v>1028</v>
+        <v>1015</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
-        <v>1029</v>
+        <v>1016</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
-        <v>1030</v>
+        <v>1017</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
-        <v>1031</v>
+        <v>1018</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
-        <v>1032</v>
+        <v>1019</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
-        <v>1033</v>
+        <v>1020</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
-        <v>1034</v>
+        <v>1021</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
+        <v>1022</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1">
+        <v>1023</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1">
+        <v>1024</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1">
+        <v>1025</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1">
+        <v>1026</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1">
+        <v>1027</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1">
+        <v>1028</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1">
+        <v>1029</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1">
+        <v>1030</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1">
+        <v>1031</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1">
+        <v>1032</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1">
+        <v>1033</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1">
+        <v>1034</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1">
         <v>1035</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>100</v>
+      <c r="C60" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2101,13 +2647,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9311664B-7025-4B3E-B6EF-B68E9E4C06CE}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.875" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="29.5" customWidth="1"/>
-    <col min="4" max="4" width="37.625" customWidth="1"/>
+    <col min="4" max="4" width="60.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -2127,7 +2673,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -2155,7 +2701,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -2168,10 +2714,10 @@
         <v>1001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E5" s="1"/>
     </row>
@@ -2181,10 +2727,10 @@
         <v>1002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -2193,10 +2739,10 @@
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>127</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -2205,12 +2751,11 @@
         <v>1004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="1"/>
+        <v>163</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
@@ -2218,12 +2763,11 @@
         <v>1005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="1"/>
+        <v>165</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
@@ -2231,12 +2775,11 @@
         <v>1006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>25</v>
+        <v>177</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="1"/>
+        <v>166</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
@@ -2244,12 +2787,11 @@
         <v>1007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>178</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" s="1"/>
+        <v>167</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
@@ -2257,12 +2799,11 @@
         <v>1008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>179</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" s="1"/>
+        <v>168</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
@@ -2270,12 +2811,11 @@
         <v>1009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" s="1"/>
+        <v>169</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
@@ -2283,12 +2823,11 @@
         <v>1010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>129</v>
+        <v>181</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E14" s="1"/>
+        <v>170</v>
+      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
@@ -2296,12 +2835,11 @@
         <v>1011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E15" s="1"/>
+        <v>171</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
@@ -2309,12 +2847,11 @@
         <v>1012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E16" s="1"/>
+        <v>172</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
@@ -2322,12 +2859,11 @@
         <v>1013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E17" s="1"/>
+        <v>173</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
@@ -2335,12 +2871,11 @@
         <v>1014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E18" s="1"/>
+        <v>174</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
@@ -2348,12 +2883,11 @@
         <v>1015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" s="1"/>
+        <v>175</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
@@ -2361,12 +2895,11 @@
         <v>1016</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E20" s="1"/>
+        <v>126</v>
+      </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
@@ -2374,23 +2907,25 @@
         <v>1017</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="E21" s="1"/>
     </row>
-    <row r="22" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>1018</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="E22" s="1"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
@@ -2398,10 +2933,10 @@
         <v>1019</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="E23" s="1"/>
     </row>
@@ -2411,10 +2946,10 @@
         <v>1020</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E24" s="1"/>
     </row>
@@ -2424,10 +2959,10 @@
         <v>1021</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E25" s="1"/>
     </row>
@@ -2437,10 +2972,10 @@
         <v>1022</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E26" s="1"/>
     </row>
@@ -2450,10 +2985,10 @@
         <v>1023</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="E27" s="1"/>
     </row>
@@ -2463,10 +2998,10 @@
         <v>1024</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="E28" s="1"/>
     </row>
@@ -2476,10 +3011,10 @@
         <v>1025</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="E29" s="1"/>
     </row>
@@ -2489,10 +3024,10 @@
         <v>1026</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>87</v>
+        <v>147</v>
       </c>
       <c r="E30" s="1"/>
     </row>
@@ -2502,10 +3037,10 @@
         <v>1027</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="E31" s="1"/>
     </row>
@@ -2515,10 +3050,10 @@
         <v>1028</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="E32" s="1"/>
     </row>
@@ -2528,10 +3063,10 @@
         <v>1029</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>56</v>
+        <v>141</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="E33" s="1"/>
     </row>
@@ -2541,25 +3076,23 @@
         <v>1030</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>57</v>
+        <v>143</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>91</v>
+        <v>151</v>
       </c>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="1"/>
+    <row r="35" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B35" s="1">
         <v>1031</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E35" s="1"/>
+        <v>116</v>
+      </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
@@ -2567,10 +3100,10 @@
         <v>1032</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E36" s="1"/>
     </row>
@@ -2580,10 +3113,10 @@
         <v>1033</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="E37" s="1"/>
     </row>
@@ -2593,10 +3126,10 @@
         <v>1034</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="E38" s="1"/>
     </row>
@@ -2606,10 +3139,10 @@
         <v>1035</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E39" s="1"/>
     </row>
@@ -2619,10 +3152,10 @@
         <v>1036</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="E40" s="1"/>
     </row>
@@ -2632,10 +3165,10 @@
         <v>1037</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="E41" s="1"/>
     </row>
@@ -2645,10 +3178,10 @@
         <v>1038</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="E42" s="1"/>
     </row>
@@ -2658,10 +3191,10 @@
         <v>1039</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="E43" s="1"/>
     </row>
@@ -2671,10 +3204,10 @@
         <v>1040</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="E44" s="1"/>
     </row>
@@ -2684,10 +3217,10 @@
         <v>1041</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E45" s="1"/>
     </row>
@@ -2697,10 +3230,10 @@
         <v>1042</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E46" s="1"/>
     </row>
@@ -2710,12 +3243,181 @@
         <v>1043</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E47" s="1"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1">
+        <v>1044</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E48" s="1"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1">
+        <v>1045</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E49" s="1"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1">
+        <v>1046</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E50" s="1"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1">
+        <v>1047</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E51" s="1"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1">
+        <v>1048</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E52" s="1"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1">
+        <v>1049</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E53" s="1"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1">
+        <v>1050</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E54" s="1"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1">
+        <v>1051</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E55" s="1"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1">
+        <v>1052</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E56" s="1"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1">
+        <v>1053</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E57" s="1"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1">
+        <v>1054</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E58" s="1"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1">
+        <v>1055</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E59" s="1"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1">
+        <v>1056</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E60" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Excel/Language.xlsx
+++ b/Excel/Language.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Unity\MightyFinalFight\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA22FB9C-762E-4E30-B8C0-336478E978BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06AC346C-BE05-4910-BF86-7B65B30EE273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9465" yWindow="1260" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SimplifiedChinese" sheetId="1" r:id="rId1"/>
@@ -632,56 +632,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>THIS IS METRO CITY.\r\nWITHIN THE WALLS OF THE\r\nCITY LIVES</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>TitlePanelStory1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>THE DAUGHTER OF THE\r\nMAYOR.JESSICA. HER\r\nBEAUTY RADI -</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>TitlePanelStory2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ATES THROUGHOUT THE\r\nCITY AND GIVES THE\r\nCITIZENS THE</t>
-  </si>
-  <si>
-    <t>POWER TO SURVIVE.BUT\r\nNOW A VILLAIN ATTEMPTS\r\nTO HAVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> THIS BEACON OF LIGHT ALL\r\nTO HIMSELF.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I CAN'T BELIEVE THAT I'VE\r\nACTUALLY FALLEN IN LOVE</t>
-  </si>
-  <si>
-    <t>WITH THE GIRL.SHE WILL\r\nBE MINE....</t>
-  </si>
-  <si>
     <t>A COUPLE DAYS LATER...</t>
   </si>
   <si>
     <t>WHAT?! JESSICA... KIDNAPPED...!?!</t>
   </si>
   <si>
-    <t>WAHT HAVE YOU DONE TO\r\nHER. CODY?</t>
-  </si>
-  <si>
-    <t>ME?!! THIS IS THE WORK OF\r\nTHE MAD GEAR GANG.</t>
-  </si>
-  <si>
     <t>WAHT DO YOU THINK. GUY?</t>
   </si>
   <si>
-    <t>YES THERE'S NOT A\r\nMOMENT TO SPARE LET'S\r\nGO!</t>
-  </si>
-  <si>
     <t>TitlePanelStory3</t>
   </si>
   <si>
@@ -865,6 +832,38 @@
   </si>
   <si>
     <t>お前なんか屁でもない！</t>
+  </si>
+  <si>
+    <t>THIS IS METRO CITY.\nWITHIN THE WALLS OF THE\nCITY LIVES</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>THE DAUGHTER OF THE\nMAYOR.JESSICA. HER\nBEAUTY RADI -</t>
+  </si>
+  <si>
+    <t>ATES THROUGHOUT THE\nCITY AND GIVES THE\nCITIZENS THE</t>
+  </si>
+  <si>
+    <t>POWER TO SURVIVE.BUT\nNOW A VILLAIN ATTEMPTS\nTO HAVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> THIS BEACON OF LIGHT ALL\nTO HIMSELF.</t>
+  </si>
+  <si>
+    <t>I CAN'T BELIEVE THAT I'VE\nACTUALLY FALLEN IN LOVE</t>
+  </si>
+  <si>
+    <t>WITH THE GIRL.SHE WILL\nBE MINE....</t>
+  </si>
+  <si>
+    <t>WAHT HAVE YOU DONE TO\nHER. CODY?</t>
+  </si>
+  <si>
+    <t>YES THERE'S NOT A\nMOMENT TO SPARE LET'S\nGO!</t>
+  </si>
+  <si>
+    <t>ME?!! THIS IS THE WORK OF\nTHE MAD GEAR GANG.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1278,10 +1277,10 @@
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1290,10 +1289,10 @@
         <v>1004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1302,10 +1301,10 @@
         <v>1005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1314,10 +1313,10 @@
         <v>1006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1326,10 +1325,10 @@
         <v>1007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1338,10 +1337,10 @@
         <v>1008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1350,10 +1349,10 @@
         <v>1009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1362,10 +1361,10 @@
         <v>1010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1374,10 +1373,10 @@
         <v>1011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1386,10 +1385,10 @@
         <v>1012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
@@ -1398,10 +1397,10 @@
         <v>1013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
@@ -1410,10 +1409,10 @@
         <v>1014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
@@ -1422,10 +1421,10 @@
         <v>1015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
@@ -1816,7 +1815,7 @@
         <v>62</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.2">
@@ -1990,10 +1989,10 @@
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -2002,10 +2001,10 @@
         <v>1004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -2014,10 +2013,10 @@
         <v>1005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -2026,10 +2025,10 @@
         <v>1006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -2038,10 +2037,10 @@
         <v>1007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -2050,10 +2049,10 @@
         <v>1008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -2062,10 +2061,10 @@
         <v>1009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
@@ -2074,10 +2073,10 @@
         <v>1010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
@@ -2086,10 +2085,10 @@
         <v>1011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
@@ -2098,10 +2097,10 @@
         <v>1012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -2110,10 +2109,10 @@
         <v>1013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -2122,10 +2121,10 @@
         <v>1014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -2134,10 +2133,10 @@
         <v>1015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -2420,7 +2419,7 @@
         <v>33</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -2432,7 +2431,7 @@
         <v>52</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
@@ -2444,7 +2443,7 @@
         <v>53</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
@@ -2456,7 +2455,7 @@
         <v>54</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
@@ -2468,7 +2467,7 @@
         <v>55</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
@@ -2480,7 +2479,7 @@
         <v>56</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
@@ -2492,7 +2491,7 @@
         <v>57</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -2504,7 +2503,7 @@
         <v>58</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
@@ -2516,7 +2515,7 @@
         <v>59</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -2528,7 +2527,7 @@
         <v>60</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -2540,7 +2539,7 @@
         <v>61</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -2552,7 +2551,7 @@
         <v>62</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -2564,7 +2563,7 @@
         <v>63</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -2576,7 +2575,7 @@
         <v>64</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
@@ -2588,7 +2587,7 @@
         <v>65</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -2600,7 +2599,7 @@
         <v>66</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -2612,7 +2611,7 @@
         <v>67</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -2624,7 +2623,7 @@
         <v>68</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -2636,7 +2635,7 @@
         <v>69</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -2739,10 +2738,10 @@
         <v>1003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>161</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -2751,10 +2750,10 @@
         <v>1004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>163</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -2763,10 +2762,10 @@
         <v>1005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>165</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -2775,10 +2774,10 @@
         <v>1006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>166</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -2787,10 +2786,10 @@
         <v>1007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>167</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -2799,10 +2798,10 @@
         <v>1008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>168</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -2811,10 +2810,10 @@
         <v>1009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>169</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -2823,10 +2822,10 @@
         <v>1010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -2835,10 +2834,10 @@
         <v>1011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -2847,10 +2846,10 @@
         <v>1012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -2859,10 +2858,10 @@
         <v>1013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>173</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -2871,10 +2870,10 @@
         <v>1014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -2883,10 +2882,10 @@
         <v>1015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>175</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">

--- a/Excel/Language.xlsx
+++ b/Excel/Language.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MightyFinalFight\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Work\Unity\MightyFinalFight\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06AC346C-BE05-4910-BF86-7B65B30EE273}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD93838F-2037-4D11-93DE-AABDF55EFA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3855" yWindow="3855" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SimplifiedChinese" sheetId="1" r:id="rId1"/>
@@ -21,9 +21,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2646,7 +2643,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9311664B-7025-4B3E-B6EF-B68E9E4C06CE}">
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.875" customWidth="1"/>
@@ -2655,7 +2652,7 @@
     <col min="4" max="4" width="60.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2668,9 +2665,8 @@
       <c r="D1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>71</v>
       </c>
@@ -2683,9 +2679,8 @@
       <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -2696,18 +2691,16 @@
       <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>100</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>1001</v>
@@ -2718,9 +2711,8 @@
       <c r="D5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1">
         <v>1002</v>
@@ -2732,7 +2724,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1">
         <v>1003</v>
@@ -2744,7 +2736,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1">
         <v>1004</v>
@@ -2756,7 +2748,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1">
         <v>1005</v>
@@ -2768,7 +2760,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1">
         <v>1006</v>
@@ -2780,7 +2772,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1">
         <v>1007</v>
@@ -2792,7 +2784,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1">
         <v>1008</v>
@@ -2804,7 +2796,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1">
         <v>1009</v>
@@ -2816,7 +2808,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1">
         <v>1010</v>
@@ -2828,7 +2820,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1">
         <v>1011</v>
@@ -2840,7 +2832,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1">
         <v>1012</v>
@@ -2852,7 +2844,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1">
         <v>1013</v>
@@ -2864,7 +2856,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1">
         <v>1014</v>
@@ -2876,7 +2868,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1">
         <v>1015</v>
@@ -2888,7 +2880,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1">
         <v>1016</v>
@@ -2900,7 +2892,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1">
         <v>1017</v>
@@ -2911,9 +2903,8 @@
       <c r="D21" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E21" s="1"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1">
         <v>1018</v>
@@ -2924,9 +2915,8 @@
       <c r="D22" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E22" s="1"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1">
         <v>1019</v>
@@ -2937,9 +2927,8 @@
       <c r="D23" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="1"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1">
         <v>1020</v>
@@ -2950,9 +2939,8 @@
       <c r="D24" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E24" s="1"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1">
         <v>1021</v>
@@ -2963,9 +2951,8 @@
       <c r="D25" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="1"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1">
         <v>1022</v>
@@ -2976,9 +2963,8 @@
       <c r="D26" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E26" s="1"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1">
         <v>1023</v>
@@ -2989,9 +2975,8 @@
       <c r="D27" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E27" s="1"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1">
         <v>1024</v>
@@ -3002,9 +2987,8 @@
       <c r="D28" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E28" s="1"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1">
         <v>1025</v>
@@ -3015,9 +2999,8 @@
       <c r="D29" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E29" s="1"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1">
         <v>1026</v>
@@ -3028,9 +3011,8 @@
       <c r="D30" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1">
         <v>1027</v>
@@ -3041,9 +3023,8 @@
       <c r="D31" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E31" s="1"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="1">
         <v>1028</v>
@@ -3054,9 +3035,8 @@
       <c r="D32" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="1">
         <v>1029</v>
@@ -3067,9 +3047,8 @@
       <c r="D33" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1">
         <v>1030</v>
@@ -3080,9 +3059,8 @@
       <c r="D34" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B35" s="1">
         <v>1031</v>
       </c>
@@ -3093,7 +3071,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1">
         <v>1032</v>
@@ -3104,9 +3082,8 @@
       <c r="D36" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E36" s="1"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1">
         <v>1033</v>
@@ -3117,9 +3094,8 @@
       <c r="D37" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E37" s="1"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1">
         <v>1034</v>
@@ -3130,9 +3106,8 @@
       <c r="D38" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E38" s="1"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1">
         <v>1035</v>
@@ -3143,9 +3118,8 @@
       <c r="D39" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1">
         <v>1036</v>
@@ -3156,9 +3130,8 @@
       <c r="D40" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E40" s="1"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1">
         <v>1037</v>
@@ -3169,9 +3142,8 @@
       <c r="D41" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E41" s="1"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="1">
         <v>1038</v>
@@ -3182,9 +3154,8 @@
       <c r="D42" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E42" s="1"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="1">
         <v>1039</v>
@@ -3195,9 +3166,8 @@
       <c r="D43" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E43" s="1"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="1">
         <v>1040</v>
@@ -3208,9 +3178,8 @@
       <c r="D44" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E44" s="1"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="1">
         <v>1041</v>
@@ -3221,9 +3190,8 @@
       <c r="D45" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E45" s="1"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="1">
         <v>1042</v>
@@ -3234,9 +3202,8 @@
       <c r="D46" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E46" s="1"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
       <c r="B47" s="1">
         <v>1043</v>
@@ -3247,9 +3214,8 @@
       <c r="D47" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E47" s="1"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="1">
         <v>1044</v>
@@ -3260,9 +3226,8 @@
       <c r="D48" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E48" s="1"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="1">
         <v>1045</v>
@@ -3273,9 +3238,8 @@
       <c r="D49" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E49" s="1"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="1">
         <v>1046</v>
@@ -3286,9 +3250,8 @@
       <c r="D50" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E50" s="1"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="1"/>
       <c r="B51" s="1">
         <v>1047</v>
@@ -3299,9 +3262,8 @@
       <c r="D51" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E51" s="1"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
       <c r="B52" s="1">
         <v>1048</v>
@@ -3312,9 +3274,8 @@
       <c r="D52" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E52" s="1"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="1">
         <v>1049</v>
@@ -3325,9 +3286,8 @@
       <c r="D53" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E53" s="1"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1">
         <v>1050</v>
@@ -3338,9 +3298,8 @@
       <c r="D54" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E54" s="1"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1">
         <v>1051</v>
@@ -3351,9 +3310,8 @@
       <c r="D55" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E55" s="1"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1">
         <v>1052</v>
@@ -3364,9 +3322,8 @@
       <c r="D56" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E56" s="1"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1">
         <v>1053</v>
@@ -3377,9 +3334,8 @@
       <c r="D57" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E57" s="1"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1">
         <v>1054</v>
@@ -3390,9 +3346,8 @@
       <c r="D58" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E58" s="1"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1">
         <v>1055</v>
@@ -3403,9 +3358,8 @@
       <c r="D59" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E59" s="1"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1">
         <v>1056</v>
@@ -3416,7 +3370,6 @@
       <c r="D60" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E60" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
